--- a/Gravedigger2026/Assets/ConfigTables/Excel/科技_科技项效果配置表_Tech_TechEffectConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/科技_科技项效果配置表_Tech_TechEffectConfig.xlsx
@@ -415,7 +415,7 @@
         <v>Tech_Root</v>
       </c>
       <c r="B2" t="str">
-        <v>DigDamage_1</v>
+        <v>DigDamage_25|DigCursorRadius_2.5</v>
       </c>
       <c r="C2" t="str">
         <v/>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/科技_科技项效果配置表_Tech_TechEffectConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/科技_科技项效果配置表_Tech_TechEffectConfig.xlsx
@@ -1,14 +1,34 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>SheetJS</Application>
+  <HyperlinksChanged>false</HyperlinksChanged>
+  <SharedDoc>false</SharedDoc>
+  <LinksUpToDate>false</LinksUpToDate>
+  <ScaleCrop>false</ScaleCrop>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>Worksheets</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>1</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="1" baseType="lpstr">
+      <vt:lpstr>Sheet1</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+</Properties>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance"/>
+</file>
+
+<file path=xl\metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
@@ -30,7 +50,7 @@
 </metadata>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
@@ -75,7 +95,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -395,7 +415,16 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <sheetData>
@@ -415,7 +444,7 @@
         <v>Tech_Root</v>
       </c>
       <c r="B2" t="str">
-        <v>DigDamage_25|DigCursorRadius_2.5</v>
+        <v>DigDamage_25|DigCursorRadius_0.6</v>
       </c>
       <c r="C2" t="str">
         <v/>
